--- a/public/assets/template/jadwal-tanding-template.xlsx
+++ b/public/assets/template/jadwal-tanding-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\simaps-ukasya\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7685DC-2953-4A10-8CB3-3DFD1B3EB1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810783E6-02B9-4A40-9F0C-A564DECBA03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7875" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
@@ -34,66 +34,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>Ukasya</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Partai</t>
   </si>
   <si>
-    <t>Tanggal</t>
-  </si>
-  <si>
     <t>Gelanggang</t>
   </si>
   <si>
     <t>Babak</t>
   </si>
   <si>
-    <t>Kelompok</t>
-  </si>
-  <si>
-    <t>Pemain Biru</t>
-  </si>
-  <si>
-    <t>Partai Biru</t>
-  </si>
-  <si>
-    <t>Pemain Merah</t>
-  </si>
-  <si>
-    <t>Partai Merah</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Pemenang</t>
-  </si>
-  <si>
-    <t>Aktif</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>Penyisihan</t>
   </si>
   <si>
-    <t>Tunggal Putra Remaja</t>
-  </si>
-  <si>
-    <t>Mustavid</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>ASAD</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>Next_Sudut</t>
+  </si>
+  <si>
+    <t>Sudut_Merah</t>
+  </si>
+  <si>
+    <t>Sudut_Biru</t>
+  </si>
+  <si>
+    <t>Next_Partai</t>
+  </si>
+  <si>
+    <t>ARENA A</t>
   </si>
 </sst>
 </file>
@@ -170,12 +137,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -508,12 +472,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -521,80 +483,50 @@
     <col min="12" max="12" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>45638</v>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
